--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2FCED1-B5E2-45D0-9461-7703E59CDD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981F17E4-5D91-4905-ADBB-B8048C88C8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>item use</t>
   </si>
@@ -102,6 +102,27 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/860020572003/5727172</t>
+  </si>
+  <si>
+    <t>Buck inductor</t>
+  </si>
+  <si>
+    <t>LC200-0185</t>
+  </si>
+  <si>
+    <t>437uH GE Inductor (Already in lab)</t>
+  </si>
+  <si>
+    <t>CAP ALUM 150UF 20% 200V RADIAL</t>
+  </si>
+  <si>
+    <t>P13520-ND</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panasonic-industry/EEU-ED2D151/1086745</t>
   </si>
 </sst>
 </file>
@@ -131,12 +152,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -152,12 +179,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -181,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H4" totalsRowShown="0">
-  <autoFilter ref="A1:H4" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H5" totalsRowShown="0">
+  <autoFilter ref="A1:H5" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
   <tableColumns count="8">
     <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use"/>
     <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description"/>
@@ -462,13 +491,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="98.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
@@ -503,90 +532,139 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>24.05</v>
-      </c>
-      <c r="H2">
-        <f t="shared" ref="H2:H3" si="0">F2*G2</f>
-        <v>72.150000000000006</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2.33</v>
+      </c>
+      <c r="H3">
+        <f>Table1[[#This Row],[quantity]]*Table1[[#This Row],[unit price]]</f>
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <f>F5*G5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>24.05</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" ref="H9:H10" si="0">F9*G9</f>
+        <v>72.150000000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D10" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3">
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G10" s="3">
         <v>9.2799999999999994</v>
       </c>
-      <c r="H3">
+      <c r="H10">
         <f t="shared" si="0"/>
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4">
+      <c r="F11" s="2">
         <v>10</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G11" s="6">
         <v>0.1</v>
       </c>
-      <c r="H4">
-        <f>F4*G4</f>
+      <c r="H11" s="2">
+        <f>F11*G11</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{834A813A-2921-4DBA-951C-4D613A5B8572}"/>
-    <hyperlink ref="E4" r:id="rId2" xr:uid="{731E9BA3-84A5-4BF3-B19A-5D7D51647ABD}"/>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{834A813A-2921-4DBA-951C-4D613A5B8572}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{731E9BA3-84A5-4BF3-B19A-5D7D51647ABD}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{E649B2B9-16DE-4CDD-9A8C-155AEF881E8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981F17E4-5D91-4905-ADBB-B8048C88C8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199AE061-4643-4FFD-ACB7-A10735BD8D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>item use</t>
   </si>
@@ -59,70 +59,67 @@
     <t>Total cost</t>
   </si>
   <si>
-    <t>Rectifier filter cap</t>
-  </si>
-  <si>
-    <t>CAP ALUM 2.7MF 20% 200V SNAP TH</t>
-  </si>
-  <si>
-    <t>B43544A2278M000</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>Buck capacitor</t>
-  </si>
-  <si>
-    <t>Würth Elektronik</t>
-  </si>
-  <si>
-    <t>Three phase rectifier</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
-    <t>Bridge Rectifiers Bridge, 3phase, DB, 200V, 15A, 150C, 350A</t>
-  </si>
-  <si>
-    <t>DB15-02</t>
-  </si>
-  <si>
-    <t>Diotec Semiconductor</t>
-  </si>
-  <si>
-    <t>https://www.mouser.com/en/ProductDetail/Diotec-Semiconductor/DB15-02?qs=OlC7AqGiEDmue9J3fser1A%3D%3D</t>
-  </si>
-  <si>
-    <t>CAP ALUM 10UF 20% 35V RADIAL TH</t>
-  </si>
-  <si>
-    <t>860020572003</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/860020572003/5727172</t>
-  </si>
-  <si>
-    <t>Buck inductor</t>
-  </si>
-  <si>
     <t>LC200-0185</t>
   </si>
   <si>
     <t>437uH GE Inductor (Already in lab)</t>
   </si>
   <si>
-    <t>CAP ALUM 150UF 20% 200V RADIAL</t>
-  </si>
-  <si>
-    <t>P13520-ND</t>
-  </si>
-  <si>
     <t>DigiKey</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/panasonic-industry/EEU-ED2D151/1086745</t>
+    <t>CAP ALUM 560UF 20% 200V SNAP TH</t>
+  </si>
+  <si>
+    <t>493-8516-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/nichicon/LGW2D561MELA30/1966872</t>
+  </si>
+  <si>
+    <t>Bridge Rectifiers 200V 30A Power Diode Discretes-FRED i4-Pac</t>
+  </si>
+  <si>
+    <t>DPF30U200FC</t>
+  </si>
+  <si>
+    <t>MOUSER</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/en/ProductDetail/IXYS/DPF30U200FC?qs=rQFj71Wb1eWHztVyBgjseQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Rectifier Capacitor</t>
+  </si>
+  <si>
+    <t>Buck Inductor</t>
+  </si>
+  <si>
+    <t>Three Phase Rectifier</t>
+  </si>
+  <si>
+    <t>Buck Capacitor</t>
+  </si>
+  <si>
+    <t>MOSFET</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>MBR10200_T0_00001</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 200V 10A TO220AC</t>
+  </si>
+  <si>
+    <t>DigikKey</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panjit-international-inc/MBR10200-T0-00001/15799461</t>
   </si>
 </sst>
 </file>
@@ -210,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H5" totalsRowShown="0">
-  <autoFilter ref="A1:H5" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H7" totalsRowShown="0">
+  <autoFilter ref="A1:H7" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
   <tableColumns count="8">
     <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use"/>
     <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description"/>
@@ -495,7 +492,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="98.44140625" bestFit="1" customWidth="1"/>
@@ -518,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -532,135 +529,146 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>5.25</v>
+      </c>
+      <c r="H2">
+        <f>Table1[[#This Row],[quantity]]*Table1[[#This Row],[unit price]]</f>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2.33</v>
+        <v>20.09</v>
       </c>
       <c r="H3">
         <f>Table1[[#This Row],[quantity]]*Table1[[#This Row],[unit price]]</f>
-        <v>9.32</v>
+        <v>20.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
       <c r="H5">
         <f>F5*G5</f>
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <f>F6*G6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1.29</v>
+      </c>
+      <c r="H7">
+        <f>F7*G7</f>
+        <v>1.29</v>
+      </c>
+    </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <v>3</v>
-      </c>
-      <c r="G9" s="2">
-        <v>24.05</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" ref="H9:H10" si="0">F9*G9</f>
-        <v>72.150000000000006</v>
-      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>9.2799999999999994</v>
-      </c>
+      <c r="E10" s="1"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="H11" s="2">
-        <f>F11*G11</f>
-        <v>1</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1" xr:uid="{834A813A-2921-4DBA-951C-4D613A5B8572}"/>
-    <hyperlink ref="E11" r:id="rId2" xr:uid="{731E9BA3-84A5-4BF3-B19A-5D7D51647ABD}"/>
-    <hyperlink ref="E3" r:id="rId3" xr:uid="{E649B2B9-16DE-4CDD-9A8C-155AEF881E8C}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{E649B2B9-16DE-4CDD-9A8C-155AEF881E8C}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{1547E749-6240-43E7-A08B-467B1DD3808B}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{DF8A8B79-7C2D-442E-AB3C-366F8EF73C57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199AE061-4643-4FFD-ACB7-A10735BD8D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C854278-E324-4385-9325-3FC1152EAE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>item use</t>
   </si>
@@ -50,9 +72,6 @@
     <t>vendor</t>
   </si>
   <si>
-    <t>quantity</t>
-  </si>
-  <si>
     <t>unit price</t>
   </si>
   <si>
@@ -116,16 +135,109 @@
     <t>DIODE SCHOTTKY 200V 10A TO220AC</t>
   </si>
   <si>
-    <t>DigikKey</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/panjit-international-inc/MBR10200-T0-00001/15799461</t>
+  </si>
+  <si>
+    <t>10 µF 50 V Aluminum Electrolytic Capacitors Radial, Can 5000 Hrs @ 105°C</t>
+  </si>
+  <si>
+    <t>EEU-FR1H100</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panasonic-industry/EEU-FR1H100/9921028</t>
+  </si>
+  <si>
+    <t>MOSFET N-CH 200V 12A TO220AB</t>
+  </si>
+  <si>
+    <t>IRF200B211</t>
+  </si>
+  <si>
+    <t>IRF200B211 Infineon Technologies | Single FETs, MOSFETs | DigiKey</t>
+  </si>
+  <si>
+    <t>Current sense IC</t>
+  </si>
+  <si>
+    <t>CURRENT SENSOR HE 10-SOIC</t>
+  </si>
+  <si>
+    <t>TMCS1133C5AQDVGR</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/TMCS1133C5AQDVGR/23331381</t>
+  </si>
+  <si>
+    <t>Generator conn</t>
+  </si>
+  <si>
+    <t>TERM BLK 3POS SIDE ENTRY 5MM PCB</t>
+  </si>
+  <si>
+    <t>OSTTA030161</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/on-shore-technology-inc/OSTTA030161/555036</t>
+  </si>
+  <si>
+    <t>Battery conn</t>
+  </si>
+  <si>
+    <t>TERM BLK 2POS SIDE ENT 3.5MM PCB</t>
+  </si>
+  <si>
+    <t>284391-2</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/284391-2/1827021</t>
+  </si>
+  <si>
+    <t>Signal conn</t>
+  </si>
+  <si>
+    <t>TERM BLK 3POS SIDE ENT 3.5MM PCB</t>
+  </si>
+  <si>
+    <t>284391-3</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/284391-3/1827022</t>
+  </si>
+  <si>
+    <t>MISC</t>
+  </si>
+  <si>
+    <t>Voltage divider resistiors and decoupling capacitors</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>min quantity</t>
+  </si>
+  <si>
+    <t>PCBs</t>
+  </si>
+  <si>
+    <t>5 pack</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>ERROR MARGIN</t>
+  </si>
+  <si>
+    <t>25% budget error margin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -143,10 +255,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -163,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -171,27 +285,170 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="11">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -207,21 +464,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H7" totalsRowShown="0">
-  <autoFilter ref="A1:H7" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
-  <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use"/>
-    <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description"/>
-    <tableColumn id="2" xr3:uid="{0F29471E-8450-4076-A11B-42E60513268E}" name="product number"/>
-    <tableColumn id="3" xr3:uid="{5235EA40-33F9-4337-B7AF-72A732137026}" name="vendor"/>
-    <tableColumn id="8" xr3:uid="{E9AD782F-B631-439F-8AEA-B1DBE224FC4B}" name="link"/>
-    <tableColumn id="4" xr3:uid="{F817B8B8-F62B-4AED-A59D-A4A7A27FEF20}" name="quantity"/>
-    <tableColumn id="5" xr3:uid="{667F21B1-6936-4832-9511-B62ACA607FAB}" name="unit price"/>
-    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost" dataDxfId="0">
-      <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:I14" totalsRowCount="1" totalsRowBorderDxfId="10">
+  <autoFilter ref="A1:I13" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
+  <tableColumns count="9">
+    <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use" totalsRowLabel="ERROR MARGIN" totalsRowDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description" totalsRowLabel="25% budget error margin" totalsRowDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{0F29471E-8450-4076-A11B-42E60513268E}" name="product number" totalsRowDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{5235EA40-33F9-4337-B7AF-72A732137026}" name="vendor" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{E9AD782F-B631-439F-8AEA-B1DBE224FC4B}" name="link" totalsRowDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{F817B8B8-F62B-4AED-A59D-A4A7A27FEF20}" name="min quantity" totalsRowDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{A74ECAB5-6866-45FE-B92D-FDDFDD7BC604}" name="Quantity" totalsRowDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{667F21B1-6936-4832-9511-B62ACA607FAB}" name="unit price" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="0">
+      <calculatedColumnFormula>F2*H2</calculatedColumnFormula>
+      <totalsRowFormula array="1">SUM(I2:I12*0.25)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -488,20 +747,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="98.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,164 +774,397 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>5.25</v>
+      <c r="G2" s="1">
+        <v>10</v>
       </c>
       <c r="H2">
-        <f>Table1[[#This Row],[quantity]]*Table1[[#This Row],[unit price]]</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3.61</v>
+      </c>
+      <c r="I2" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
+        <v>3</v>
+      </c>
+      <c r="H3">
         <v>20.09</v>
       </c>
-      <c r="H3">
-        <f>Table1[[#This Row],[quantity]]*Table1[[#This Row],[unit price]]</f>
-        <v>20.09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>60.269999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="H5">
-        <f>F5*G5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>2.23</v>
+      </c>
+      <c r="I6" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="H6">
-        <f>F6*G6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7">
-        <v>1.29</v>
+      <c r="G7" s="1">
+        <v>10</v>
       </c>
       <c r="H7">
-        <f>F7*G7</f>
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E10" s="1"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>4.07</v>
+      </c>
+      <c r="I8" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>20.350000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="I9" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="I10" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>9.3999999999999986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1.78</v>
+      </c>
+      <c r="I11" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>70</v>
+      </c>
+      <c r="I12" s="6">
+        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13" s="6">
+        <f>F13*H13</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="11" cm="1">
+        <f t="array" ref="I14">SUM(I2:I12*0.25)</f>
+        <v>58.505000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9">
+        <f>SUM(Table1[[#Data],[#Totals],[Total cost]])</f>
+        <v>302.52500000000003</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{E649B2B9-16DE-4CDD-9A8C-155AEF881E8C}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{1547E749-6240-43E7-A08B-467B1DD3808B}"/>
     <hyperlink ref="E7" r:id="rId3" xr:uid="{DF8A8B79-7C2D-442E-AB3C-366F8EF73C57}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{E900A9BE-DEBC-4814-95FE-2AD5B631E768}"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://www.digikey.com/en/products/detail/infineon-technologies/IRF200B211/5250541" xr:uid="{92A05147-8B45-4DF8-BD2B-4B39BD974BA9}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{3F587FE5-E467-419A-8BC3-047E2E106230}"/>
+    <hyperlink ref="E9" r:id="rId7" xr:uid="{EE88AA29-0BDA-4628-977F-3EEB44D8A876}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{FEAC75F6-09B5-4E6F-A980-6D6DB88FD482}"/>
+    <hyperlink ref="E11" r:id="rId9" xr:uid="{10DB1139-32B6-48E2-A6D4-4A8AA715BEDF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C854278-E324-4385-9325-3FC1152EAE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1B8A6-DC75-4A82-A7A3-0F5705D0E804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -174,12 +174,6 @@
     <t>TERM BLK 3POS SIDE ENTRY 5MM PCB</t>
   </si>
   <si>
-    <t>OSTTA030161</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/on-shore-technology-inc/OSTTA030161/555036</t>
-  </si>
-  <si>
     <t>Battery conn</t>
   </si>
   <si>
@@ -229,6 +223,12 @@
   </si>
   <si>
     <t>25% budget error margin</t>
+  </si>
+  <si>
+    <t>277-1578-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/phoenix-contact/1935174/568615</t>
   </si>
 </sst>
 </file>
@@ -777,10 +777,10 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -995,13 +995,13 @@
         <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -1010,28 +1010,28 @@
         <v>5</v>
       </c>
       <c r="H9" s="2">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="I9" s="6">
         <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>4.8499999999999996</v>
+        <v>3.5999999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
         <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -1049,19 +1049,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1131,12 +1131,12 @@
       <c r="H14" s="7"/>
       <c r="I14" s="11" cm="1">
         <f t="array" ref="I14">SUM(I2:I12*0.25)</f>
-        <v>58.505000000000003</v>
+        <v>58.192500000000003</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -1147,7 +1147,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="9">
         <f>SUM(Table1[[#Data],[#Totals],[Total cost]])</f>
-        <v>302.52500000000003</v>
+        <v>300.96250000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1B8A6-DC75-4A82-A7A3-0F5705D0E804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6FB56B-F1DE-4E17-BABA-A482FA3B2ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Suggested" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
   <si>
     <t>item use</t>
   </si>
@@ -219,16 +219,52 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>ERROR MARGIN</t>
-  </si>
-  <si>
-    <t>25% budget error margin</t>
-  </si>
-  <si>
     <t>277-1578-ND</t>
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/phoenix-contact/1935174/568615</t>
+  </si>
+  <si>
+    <t>MCU board</t>
+  </si>
+  <si>
+    <t>F28379D LaunchPad™ development kit for C2000™ Delfino™ MCU</t>
+  </si>
+  <si>
+    <t>LAUNCHXL-F28379D</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>Gate driver eval board</t>
+  </si>
+  <si>
+    <t>EVAL BOARD FOR STGAP2HDM</t>
+  </si>
+  <si>
+    <t>EVALSTGAP2HDM</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/stmicroelectronics/EVALSTGAP2HDM/</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/tool/LAUNCHXL-F28379D</t>
+  </si>
+  <si>
+    <t>TOTAL excluding PCBs</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Estimate of shipping for components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency </t>
+  </si>
+  <si>
+    <t>20% contingency</t>
   </si>
 </sst>
 </file>
@@ -238,7 +274,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +298,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -272,12 +316,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -286,26 +330,233 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -314,104 +565,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="7">
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
         <bottom/>
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
-          <color theme="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
-          <color theme="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -431,23 +697,55 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
-          <color theme="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color theme="1"/>
+          <color indexed="64"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -464,23 +762,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:I14" totalsRowCount="1" totalsRowBorderDxfId="10">
-  <autoFilter ref="A1:I13" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D59A0370-B28F-4833-BBF6-73CA5F258DAA}" name="Table10" displayName="Table10" ref="A1:I19" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+  <autoFilter ref="A1:I19" xr:uid="{D59A0370-B28F-4833-BBF6-73CA5F258DAA}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use" totalsRowLabel="ERROR MARGIN" totalsRowDxfId="8"/>
-    <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description" totalsRowLabel="25% budget error margin" totalsRowDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{0F29471E-8450-4076-A11B-42E60513268E}" name="product number" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{5235EA40-33F9-4337-B7AF-72A732137026}" name="vendor" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{E9AD782F-B631-439F-8AEA-B1DBE224FC4B}" name="link" totalsRowDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{F817B8B8-F62B-4AED-A59D-A4A7A27FEF20}" name="min quantity" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{A74ECAB5-6866-45FE-B92D-FDDFDD7BC604}" name="Quantity" totalsRowDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{667F21B1-6936-4832-9511-B62ACA607FAB}" name="unit price" totalsRowDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="0">
-      <calculatedColumnFormula>F2*H2</calculatedColumnFormula>
-      <totalsRowFormula array="1">SUM(I2:I12*0.25)</totalsRowFormula>
-    </tableColumn>
+    <tableColumn id="1" xr3:uid="{A671E009-E1D1-415B-AB06-EBE4E463EC9A}" name="item use" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{332D8203-1DEB-4D23-ABFF-7DDE266D779A}" name="Item description" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{95FDF01E-D6FB-462C-A67F-6650D8DA5A69}" name="product number" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{D4E2AD05-99DD-45B5-AF98-5F14CE702324}" name="vendor"/>
+    <tableColumn id="5" xr3:uid="{0EE3A759-7F48-4DA9-967C-886AD9B2FF61}" name="link"/>
+    <tableColumn id="6" xr3:uid="{79309A75-CAC8-4BB4-B390-BF5EE7718A07}" name="min quantity"/>
+    <tableColumn id="7" xr3:uid="{14865014-C08A-4EF3-88DE-ED13C35C43CB}" name="Quantity"/>
+    <tableColumn id="8" xr3:uid="{27596AD4-FD25-425D-844E-0F45D97ADE84}" name="unit price"/>
+    <tableColumn id="9" xr3:uid="{219B9DC7-A358-492B-9068-479CD40DD8B0}" name="Total cost"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -747,407 +1042,515 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="66.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="98.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" customWidth="1"/>
     <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="3">
         <v>10</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>3.61</v>
       </c>
-      <c r="I2" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+      <c r="I2" s="4">
+        <f>Suggested!$H2*Suggested!$G2</f>
         <v>36.1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2">
+        <v>20.09</v>
+      </c>
+      <c r="I3" s="4">
+        <f>Suggested!$H3*Suggested!$G3</f>
+        <v>40.18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="4">
+        <f>Suggested!$H4*Suggested!$G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="4">
+        <f>Suggested!$H5*Suggested!$G5</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
         <v>3</v>
       </c>
-      <c r="H3">
-        <v>20.09</v>
-      </c>
-      <c r="I3" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>60.269999999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="H6" s="2">
+        <v>2.23</v>
+      </c>
+      <c r="I6" s="4">
+        <f>Suggested!$H6*Suggested!$G6</f>
+        <v>6.6899999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>0.25</v>
-      </c>
-      <c r="I5" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1.29</v>
+      </c>
+      <c r="I7" s="4">
+        <f>Suggested!$H7*Suggested!$G7</f>
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>2.23</v>
-      </c>
-      <c r="I6" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>11.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>0.8</v>
-      </c>
-      <c r="I7" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>4.07</v>
-      </c>
-      <c r="I8" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>20.350000000000001</v>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>4.55</v>
+      </c>
+      <c r="I8" s="4">
+        <f>Suggested!$H8*Suggested!$G8</f>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>56</v>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="5">
-        <v>5</v>
+      <c r="G9" s="3">
+        <v>2</v>
       </c>
       <c r="H9" s="2">
         <v>0.72</v>
       </c>
-      <c r="I9" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>3.5999999999999996</v>
+      <c r="I9" s="4">
+        <f>Suggested!$H9*Suggested!$G9</f>
+        <v>1.44</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>4</v>
       </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="I10" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>9.3999999999999986</v>
+      <c r="G10" s="3">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1.94</v>
+      </c>
+      <c r="I10" s="4">
+        <f>Suggested!$H10*Suggested!$G10</f>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="5">
-        <v>5</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
         <v>1.78</v>
       </c>
-      <c r="I11" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
-        <v>8.9</v>
+      <c r="I11" s="4">
+        <f>Suggested!$H11*Suggested!$G11</f>
+        <v>3.56</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>42.9</v>
+      </c>
+      <c r="I12" s="4">
+        <f>F12*H12</f>
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>100.01</v>
+      </c>
+      <c r="I13" s="4">
+        <f>F13*H13</f>
+        <v>100.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
         <v>70</v>
       </c>
-      <c r="I12" s="6">
-        <f>Table1[[#This Row],[unit price]]*Table1[[#This Row],[Quantity]]</f>
+      <c r="I14" s="4">
+        <f>Suggested!$H14*Suggested!$G14</f>
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="H13">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="I13" s="6">
-        <f>F13*H13</f>
+      <c r="I15" s="4">
+        <f>F15*H15</f>
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="11" cm="1">
-        <f t="array" ref="I14">SUM(I2:I12*0.25)</f>
-        <v>58.192500000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="7">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19">
+        <v>1</v>
+      </c>
+      <c r="I16" s="20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="22" cm="1">
+        <f t="array" ref="I17">SUM(I2:I16*0.2)</f>
+        <v>75.210000000000008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9">
-        <f>SUM(Table1[[#Data],[#Totals],[Total cost]])</f>
-        <v>300.96250000000003</v>
+      <c r="B18" s="25"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="12">
+        <f>SUM($I$2:$I$17)</f>
+        <v>451.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="24">
+        <f>SUM(I2:I13,I15:I16)+(0.2*SUM(I15:I16,I2:I13))</f>
+        <v>367.26</v>
       </c>
     </row>
   </sheetData>
@@ -1161,10 +1564,12 @@
     <hyperlink ref="E9" r:id="rId7" xr:uid="{EE88AA29-0BDA-4628-977F-3EEB44D8A876}"/>
     <hyperlink ref="E10" r:id="rId8" xr:uid="{FEAC75F6-09B5-4E6F-A980-6D6DB88FD482}"/>
     <hyperlink ref="E11" r:id="rId9" xr:uid="{10DB1139-32B6-48E2-A6D4-4A8AA715BEDF}"/>
+    <hyperlink ref="E12" r:id="rId10" location="order-start-development" xr:uid="{7AD4C1B8-63E7-4377-85EC-8A96DCA2AFB6}"/>
+    <hyperlink ref="E13" r:id="rId11" xr:uid="{4015C2B4-E3CC-4733-A976-F575AB483C4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>